--- a/Calculator Testing.xlsx
+++ b/Calculator Testing.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shreya Jaiswal\ST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4d074a6daeb2859c/Desktop/Pooja/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_8A37EBAAD63BA00A475DA150EC1CC81F27D62196" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17EE7F66-8C1C-4717-B99B-1166BBAEFA59}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14475" windowHeight="9330"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -80,9 +81,6 @@
   </si>
   <si>
     <t>1.0</t>
-  </si>
-  <si>
-    <t>Shreya Jaiswal</t>
   </si>
   <si>
     <t>Windows Operating System</t>
@@ -243,11 +241,14 @@
   <si>
     <t xml:space="preserve">Click "CE" </t>
   </si>
+  <si>
+    <t>pooja belsare</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
@@ -625,7 +626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="54">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -698,20 +699,52 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -721,47 +754,15 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -797,7 +798,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="File:Windows Calculator icon.png - Wikimedia Commons"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="File:Windows Calculator icon.png - Wikimedia Commons">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -850,7 +857,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -905,7 +918,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -943,7 +962,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -981,7 +1006,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7"/>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1019,7 +1050,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1057,7 +1094,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9"/>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1095,7 +1138,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1132,7 +1181,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11"/>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1155,10 +1210,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1358,7 +1409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1376,10 +1427,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="42"/>
       <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
@@ -1387,13 +1438,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="32"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1411,25 +1462,25 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
+      <c r="B2" s="36"/>
       <c r="C2" s="5" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="26" t="s">
-        <v>71</v>
+      <c r="F2" s="30" t="s">
+        <v>70</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="34" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="27"/>
+      <c r="I2" s="36"/>
       <c r="J2" s="8" t="s">
         <v>19</v>
       </c>
@@ -1450,21 +1501,21 @@
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="34" t="s">
+      <c r="F3" s="49"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="27"/>
+      <c r="I3" s="36"/>
       <c r="J3" s="9"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -1513,21 +1564,21 @@
       <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="27"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="37"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="31"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1548,19 +1599,19 @@
       <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>21</v>
+      <c r="B6" s="30" t="s">
+        <v>20</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="27"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="5"/>
       <c r="F6" s="17">
         <v>1</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="31"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1581,19 +1632,19 @@
       <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>22</v>
+      <c r="B7" s="30" t="s">
+        <v>21</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="27"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="5"/>
       <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="31"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1614,17 +1665,17 @@
       <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="27"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="5"/>
       <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="31"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1645,17 +1696,17 @@
       <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="41"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="33"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="39"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="42"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="38"/>
       <c r="K9" s="21"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1703,17 +1754,17 @@
       <c r="A11" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="43" t="s">
-        <v>23</v>
+      <c r="B11" s="51" t="s">
+        <v>22</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1732,15 +1783,15 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1788,23 +1839,23 @@
       <c r="A14" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="46" t="s">
+      <c r="C14" s="42"/>
+      <c r="D14" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="46" t="s">
+      <c r="E14" s="42"/>
+      <c r="F14" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="46" t="s">
+      <c r="G14" s="43"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="32"/>
+      <c r="J14" s="44"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1825,19 +1876,19 @@
       <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>72</v>
+      <c r="B15" s="30" t="s">
+        <v>71</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="26" t="s">
-        <v>24</v>
+      <c r="C15" s="36"/>
+      <c r="D15" s="30" t="s">
+        <v>23</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="37"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="31"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1858,19 +1909,19 @@
       <c r="A16" s="16">
         <v>2</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="36"/>
+      <c r="D16" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="37"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="31"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="N16"/>
@@ -1890,19 +1941,19 @@
       <c r="A17" s="16">
         <v>3</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="26" t="s">
+      <c r="B17" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="37"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="36"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="31"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1923,19 +1974,19 @@
       <c r="A18" s="16">
         <v>4</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="36"/>
+      <c r="D18" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="37"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="31"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -1956,19 +2007,19 @@
       <c r="A19" s="16">
         <v>5</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="36"/>
+      <c r="D19" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="37"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="31"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -1989,19 +2040,19 @@
       <c r="A20" s="16">
         <v>6</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="36"/>
+      <c r="D20" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="37"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="31"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2022,19 +2073,19 @@
       <c r="A21" s="16">
         <v>7</v>
       </c>
-      <c r="B21" s="47" t="s">
-        <v>58</v>
+      <c r="B21" s="39" t="s">
+        <v>57</v>
       </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="26" t="s">
-        <v>36</v>
+      <c r="C21" s="40"/>
+      <c r="D21" s="30" t="s">
+        <v>35</v>
       </c>
-      <c r="E21" s="27"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="37"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="31"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2055,19 +2106,19 @@
       <c r="A22" s="16">
         <v>8</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>73</v>
+      <c r="B22" s="30" t="s">
+        <v>72</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="26" t="s">
-        <v>37</v>
+      <c r="C22" s="36"/>
+      <c r="D22" s="30" t="s">
+        <v>36</v>
       </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="37"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="31"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2088,19 +2139,19 @@
       <c r="A23" s="16">
         <v>9</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="37"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="31"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2121,19 +2172,19 @@
       <c r="A24" s="16">
         <v>10</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="37"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="31"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2154,19 +2205,19 @@
       <c r="A25" s="16">
         <v>11</v>
       </c>
-      <c r="B25" s="26" t="s">
-        <v>25</v>
+      <c r="B25" s="30" t="s">
+        <v>24</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="26" t="s">
-        <v>42</v>
+      <c r="C25" s="36"/>
+      <c r="D25" s="30" t="s">
+        <v>41</v>
       </c>
-      <c r="E25" s="27"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="37"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="31"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2187,19 +2238,19 @@
       <c r="A26" s="16">
         <v>12</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="36"/>
+      <c r="D26" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="27"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="37"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="31"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2220,19 +2271,19 @@
       <c r="A27" s="16">
         <v>13</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>43</v>
+      <c r="B27" s="30" t="s">
+        <v>42</v>
       </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="26" t="s">
-        <v>37</v>
+      <c r="C27" s="36"/>
+      <c r="D27" s="30" t="s">
+        <v>36</v>
       </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="37"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="31"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2253,19 +2304,19 @@
       <c r="A28" s="16">
         <v>14</v>
       </c>
-      <c r="B28" s="26" t="s">
-        <v>61</v>
+      <c r="B28" s="30" t="s">
+        <v>60</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="26" t="s">
-        <v>46</v>
+      <c r="C28" s="36"/>
+      <c r="D28" s="30" t="s">
+        <v>45</v>
       </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="37"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="31"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2286,19 +2337,19 @@
       <c r="A29" s="16">
         <v>15</v>
       </c>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="36"/>
+      <c r="D29" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="27"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="37"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="31"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2319,19 +2370,19 @@
       <c r="A30" s="16">
         <v>16</v>
       </c>
-      <c r="B30" s="26" t="s">
-        <v>49</v>
+      <c r="B30" s="30" t="s">
+        <v>48</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="26" t="s">
-        <v>62</v>
+      <c r="C30" s="36"/>
+      <c r="D30" s="30" t="s">
+        <v>61</v>
       </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="37"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="31"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2352,19 +2403,19 @@
       <c r="A31" s="16">
         <v>17</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="36"/>
+      <c r="D31" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="27"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="37"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="31"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2385,19 +2436,19 @@
       <c r="A32" s="16">
         <v>18</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="36"/>
+      <c r="D32" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="27"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="37"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="31"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2418,19 +2469,19 @@
       <c r="A33" s="16">
         <v>19</v>
       </c>
-      <c r="B33" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="26" t="s">
+      <c r="B33" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="52"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="53"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="37"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="29"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2451,19 +2502,19 @@
       <c r="A34" s="16">
         <v>20</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="37"/>
+      <c r="D34" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="52"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="53"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="29"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -2484,19 +2535,19 @@
       <c r="A35" s="16">
         <v>21</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="37"/>
+      <c r="D35" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="52"/>
-      <c r="D35" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="53"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="29"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
@@ -2517,19 +2568,19 @@
       <c r="A36" s="16">
         <v>22</v>
       </c>
-      <c r="B36" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="26" t="s">
+      <c r="B36" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="52"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="53"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36" s="37"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="29"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
@@ -2550,19 +2601,19 @@
       <c r="A37" s="16">
         <v>23</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E37" s="52"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="53"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="29"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
@@ -2583,19 +2634,19 @@
       <c r="A38" s="16">
         <v>24</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="D38" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="27"/>
-      <c r="D38" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="27"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="37"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="31"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
@@ -2616,19 +2667,19 @@
       <c r="A39" s="16">
         <v>25</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="33"/>
+      <c r="D39" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" s="41"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="42"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="38"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
@@ -28567,21 +28618,91 @@
     </row>
   </sheetData>
   <mergeCells count="124">
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="F38:H38"/>
@@ -28606,91 +28727,21 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
